--- a/pacenote_view.xlsx
+++ b/pacenote_view.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\devfiles\auto_media_pack_acg\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B163406-D167-444C-AB17-495FC344A8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8976"/>
+    <workbookView xWindow="144" yWindow="1296" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pacenote_view_202412300958" sheetId="2" r:id="rId1"/>
@@ -26,14 +32,17 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="Query - pacenote_view_202412300958" description="Connection to the 'pacenote_view_202412300958' query in the workbook." type="5" background="1" refreshedVersion="2" saveData="1">
-    <dbPr connection="Provider=Microsoft.Mashup.OleDb.1;Data Source=$Workbook$;Location=pacenote_view_202412300958;Extended Properties=&quot;&quot;" command="SELECT * FROM [pacenote_view_202412300958]" commandType="2"/>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="Query - pacenote_view_202412300958" description="Connection to the 'pacenote_view_202412300958' query in the workbook." type="5" refreshedVersion="2" background="1" saveData="1">
+    <dbPr connection="Provider=Microsoft.Mashup.OleDb.1;Data Source=$Workbook$;Location=pacenote_view_202412300958;Extended Properties=&quot;&quot;" command="SELECT * FROM [pacenote_view_202412300958]"/>
   </connection>
 </connections>
 </file>
@@ -899,9 +908,6 @@
     <t>brake,detail_brake</t>
   </si>
   <si>
-    <t>刹车</t>
-  </si>
-  <si>
     <t>DRIVING</t>
   </si>
   <si>
@@ -1082,9 +1088,6 @@
     <t>dab,detail_dab</t>
   </si>
   <si>
-    <t>点刹</t>
-  </si>
-  <si>
     <t>deceptive</t>
   </si>
   <si>
@@ -1598,9 +1601,6 @@
     <t>handbrake,detail_handbrake</t>
   </si>
   <si>
-    <t>手刹</t>
-  </si>
-  <si>
     <t>hard</t>
   </si>
   <si>
@@ -3504,19 +3504,22 @@
   </si>
   <si>
     <t>变宽</t>
+  </si>
+  <si>
+    <t>杀车</t>
+  </si>
+  <si>
+    <t>点杀</t>
+  </si>
+  <si>
+    <t>手杀</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3525,352 +3528,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -3878,306 +3550,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -4204,13 +3586,16 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_1" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh preserveSortFilterLayout="1" nextId="8">
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{00000000-0016-0000-0000-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+  <queryTableRefresh nextId="8">
     <queryTableFields count="7">
       <queryTableField id="1" name="id" tableColumnId="1"/>
       <queryTableField id="2" name="primary_filename" tableColumnId="2"/>
@@ -4225,16 +3610,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="pacenote_view_202412300958" displayName="pacenote_view_202412300958" ref="A1:G347" tableType="queryTable" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G347" etc:filterBottomFollowUsedRange="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="pacenote_view_202412300958" displayName="pacenote_view_202412300958" ref="A1:G347" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G347" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="id" uniqueName="1" queryTableFieldId="1"/>
-    <tableColumn id="2" name="primary_filename" uniqueName="2" queryTableFieldId="2" dataDxfId="0"/>
-    <tableColumn id="3" name="filenames" uniqueName="3" queryTableFieldId="3" dataDxfId="1"/>
-    <tableColumn id="4" name="description" uniqueName="4" queryTableFieldId="4" dataDxfId="2"/>
-    <tableColumn id="5" name="type" uniqueName="5" queryTableFieldId="5" dataDxfId="3"/>
-    <tableColumn id="6" name="complexity" uniqueName="6" queryTableFieldId="6" dataDxfId="4"/>
-    <tableColumn id="7" name="fallbacks" uniqueName="7" queryTableFieldId="7" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" uniqueName="1" name="id" queryTableFieldId="1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" uniqueName="2" name="primary_filename" queryTableFieldId="2" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" uniqueName="3" name="filenames" queryTableFieldId="3" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" uniqueName="4" name="description" queryTableFieldId="4" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" uniqueName="5" name="type" queryTableFieldId="5" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" uniqueName="6" name="complexity" queryTableFieldId="6" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" uniqueName="7" name="fallbacks" queryTableFieldId="7" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4512,25 +3897,25 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G347"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.84259259259259" customWidth="1"/>
-    <col min="2" max="2" width="17.9259259259259" customWidth="1"/>
-    <col min="3" max="3" width="60.1481481481481" customWidth="1"/>
-    <col min="4" max="4" width="21.6944444444444" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" customWidth="1"/>
+    <col min="3" max="3" width="60.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="12.3055555555556" customWidth="1"/>
-    <col min="7" max="7" width="17.3055555555556" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4553,7 +3938,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>299</v>
       </c>
@@ -4576,7 +3961,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>257</v>
       </c>
@@ -4599,7 +3984,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>258</v>
       </c>
@@ -4622,7 +4007,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>259</v>
       </c>
@@ -4645,7 +4030,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>260</v>
       </c>
@@ -4668,7 +4053,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>261</v>
       </c>
@@ -4691,7 +4076,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>262</v>
       </c>
@@ -4714,7 +4099,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>263</v>
       </c>
@@ -4737,7 +4122,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>264</v>
       </c>
@@ -4760,7 +4145,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>265</v>
       </c>
@@ -4783,7 +4168,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>266</v>
       </c>
@@ -4806,7 +4191,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>267</v>
       </c>
@@ -4829,7 +4214,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0</v>
       </c>
@@ -4852,7 +4237,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1</v>
       </c>
@@ -4875,7 +4260,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>300</v>
       </c>
@@ -4898,7 +4283,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>268</v>
       </c>
@@ -4921,7 +4306,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>269</v>
       </c>
@@ -4944,7 +4329,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>270</v>
       </c>
@@ -4967,7 +4352,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>271</v>
       </c>
@@ -4990,7 +4375,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>272</v>
       </c>
@@ -5013,7 +4398,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>273</v>
       </c>
@@ -5036,7 +4421,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>274</v>
       </c>
@@ -5059,7 +4444,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>275</v>
       </c>
@@ -5082,7 +4467,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>276</v>
       </c>
@@ -5105,7 +4490,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>277</v>
       </c>
@@ -5128,7 +4513,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>278</v>
       </c>
@@ -5151,7 +4536,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2</v>
       </c>
@@ -5174,7 +4559,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>3</v>
       </c>
@@ -5197,7 +4582,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>301</v>
       </c>
@@ -5220,7 +4605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>279</v>
       </c>
@@ -5243,7 +4628,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>280</v>
       </c>
@@ -5266,7 +4651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>281</v>
       </c>
@@ -5289,7 +4674,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>4</v>
       </c>
@@ -5312,7 +4697,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>5</v>
       </c>
@@ -5335,7 +4720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>302</v>
       </c>
@@ -5358,7 +4743,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>282</v>
       </c>
@@ -5381,7 +4766,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>283</v>
       </c>
@@ -5404,7 +4789,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>284</v>
       </c>
@@ -5427,7 +4812,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>6</v>
       </c>
@@ -5450,7 +4835,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>7</v>
       </c>
@@ -5473,7 +4858,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>303</v>
       </c>
@@ -5496,7 +4881,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>285</v>
       </c>
@@ -5519,7 +4904,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>286</v>
       </c>
@@ -5542,7 +4927,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8</v>
       </c>
@@ -5565,7 +4950,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9</v>
       </c>
@@ -5588,7 +4973,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>304</v>
       </c>
@@ -5611,7 +4996,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>287</v>
       </c>
@@ -5634,7 +5019,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>288</v>
       </c>
@@ -5657,7 +5042,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>10</v>
       </c>
@@ -5680,7 +5065,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>11</v>
       </c>
@@ -5703,7 +5088,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>305</v>
       </c>
@@ -5726,7 +5111,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>289</v>
       </c>
@@ -5749,7 +5134,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>290</v>
       </c>
@@ -5772,7 +5157,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>318</v>
       </c>
@@ -5795,7 +5180,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>319</v>
       </c>
@@ -5818,7 +5203,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>291</v>
       </c>
@@ -5841,7 +5226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>292</v>
       </c>
@@ -5864,7 +5249,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>293</v>
       </c>
@@ -5887,7 +5272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>294</v>
       </c>
@@ -5910,7 +5295,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>12</v>
       </c>
@@ -5933,7 +5318,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>28</v>
       </c>
@@ -5956,7 +5341,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>29</v>
       </c>
@@ -5979,7 +5364,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>30</v>
       </c>
@@ -6002,7 +5387,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>31</v>
       </c>
@@ -6025,7 +5410,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>32</v>
       </c>
@@ -6048,7 +5433,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>333</v>
       </c>
@@ -6071,7 +5456,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>329</v>
       </c>
@@ -6094,7 +5479,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>33</v>
       </c>
@@ -6117,7 +5502,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>331</v>
       </c>
@@ -6140,7 +5525,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>34</v>
       </c>
@@ -6163,7 +5548,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>332</v>
       </c>
@@ -6186,7 +5571,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>326</v>
       </c>
@@ -6209,7 +5594,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>35</v>
       </c>
@@ -6232,7 +5617,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>36</v>
       </c>
@@ -6255,7 +5640,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>37</v>
       </c>
@@ -6278,7 +5663,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>38</v>
       </c>
@@ -6301,7 +5686,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>39</v>
       </c>
@@ -6324,7 +5709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>40</v>
       </c>
@@ -6347,7 +5732,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>41</v>
       </c>
@@ -6370,7 +5755,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>42</v>
       </c>
@@ -6393,7 +5778,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>43</v>
       </c>
@@ -6416,7 +5801,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>44</v>
       </c>
@@ -6439,7 +5824,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>45</v>
       </c>
@@ -6462,7 +5847,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>46</v>
       </c>
@@ -6473,11 +5858,11 @@
         <v>285</v>
       </c>
       <c r="D85" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="F85" s="1" t="s">
         <v>11</v>
       </c>
@@ -6485,22 +5870,22 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>47</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="F86" s="1" t="s">
         <v>11</v>
       </c>
@@ -6508,18 +5893,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>48</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>208</v>
@@ -6531,18 +5916,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>49</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>208</v>
@@ -6554,18 +5939,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>50</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>208</v>
@@ -6577,18 +5962,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>51</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="D90" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>249</v>
@@ -6600,44 +5985,44 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>52</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>173</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>53</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="D92" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>11</v>
@@ -6646,18 +6031,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>54</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>208</v>
@@ -6669,18 +6054,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>55</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>208</v>
@@ -6689,25 +6074,25 @@
         <v>173</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>56</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="D95" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="E95" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E95" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="F95" s="1" t="s">
         <v>11</v>
       </c>
@@ -6715,22 +6100,22 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1009</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="F96" s="1" t="s">
         <v>11</v>
       </c>
@@ -6738,21 +6123,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>1010</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="D97" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="E97" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>11</v>
@@ -6761,21 +6146,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>1008</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="D98" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>11</v>
@@ -6784,21 +6169,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>57</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>11</v>
@@ -6807,18 +6192,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>58</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>336</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>245</v>
@@ -6830,18 +6215,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>59</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="D101" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>208</v>
@@ -6853,18 +6238,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>60</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="D102" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>208</v>
@@ -6876,18 +6261,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>61</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C103" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>344</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>275</v>
@@ -6899,21 +6284,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>62</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="D104" s="1" t="s">
-        <v>347</v>
+        <v>1153</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>173</v>
@@ -6922,21 +6307,21 @@
         <v>284</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>63</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>11</v>
@@ -6945,18 +6330,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>64</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>353</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>245</v>
@@ -6968,18 +6353,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>65</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>249</v>
@@ -6991,18 +6376,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>66</v>
       </c>
       <c r="B108" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>245</v>
@@ -7014,21 +6399,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>67</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>11</v>
@@ -7037,41 +6422,41 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>68</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="E110" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="F110" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="G110" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>69</v>
       </c>
       <c r="B111" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>208</v>
@@ -7083,18 +6468,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>70</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>208</v>
@@ -7103,21 +6488,21 @@
         <v>209</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>71</v>
       </c>
       <c r="B113" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>208</v>
@@ -7126,21 +6511,21 @@
         <v>209</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>72</v>
       </c>
       <c r="B114" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>275</v>
@@ -7152,18 +6537,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>13</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>50</v>
@@ -7175,18 +6560,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>73</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>387</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>245</v>
@@ -7198,41 +6583,41 @@
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>74</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>209</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>75</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>394</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>249</v>
@@ -7244,18 +6629,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>76</v>
       </c>
       <c r="B119" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>275</v>
@@ -7267,18 +6652,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>77</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>249</v>
@@ -7290,18 +6675,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>78</v>
       </c>
       <c r="B121" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>249</v>
@@ -7310,21 +6695,21 @@
         <v>209</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>79</v>
       </c>
       <c r="B122" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>249</v>
@@ -7333,24 +6718,24 @@
         <v>209</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>80</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="E123" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>11</v>
@@ -7359,18 +6744,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>81</v>
       </c>
       <c r="B124" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>275</v>
@@ -7382,18 +6767,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>82</v>
       </c>
       <c r="B125" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>417</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>245</v>
@@ -7405,18 +6790,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>83</v>
       </c>
       <c r="B126" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>208</v>
@@ -7428,21 +6813,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>1001</v>
       </c>
       <c r="B127" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>423</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>11</v>
@@ -7451,18 +6836,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>84</v>
       </c>
       <c r="B128" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>426</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>275</v>
@@ -7474,18 +6859,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>85</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>429</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>245</v>
@@ -7497,18 +6882,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>86</v>
       </c>
       <c r="B130" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>275</v>
@@ -7520,18 +6905,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>296</v>
       </c>
       <c r="B131" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>435</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>245</v>
@@ -7543,67 +6928,67 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>87</v>
       </c>
       <c r="B132" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="E132" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>439</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>209</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>88</v>
       </c>
       <c r="B133" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>209</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>89</v>
       </c>
       <c r="B134" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="E134" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>11</v>
@@ -7612,18 +6997,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>90</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>208</v>
@@ -7635,18 +7020,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>91</v>
       </c>
       <c r="B136" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>453</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>208</v>
@@ -7655,21 +7040,21 @@
         <v>209</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>92</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>208</v>
@@ -7678,44 +7063,44 @@
         <v>209</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>93</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>173</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>94</v>
       </c>
       <c r="B139" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>201</v>
@@ -7727,18 +7112,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>95</v>
       </c>
       <c r="B140" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>467</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>208</v>
@@ -7750,21 +7135,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>96</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>11</v>
@@ -7773,7 +7158,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>14</v>
       </c>
@@ -7781,10 +7166,10 @@
         <v>174</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>50</v>
@@ -7796,7 +7181,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>15</v>
       </c>
@@ -7804,10 +7189,10 @@
         <v>178</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>50</v>
@@ -7819,18 +7204,18 @@
         <v>158</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>97</v>
       </c>
       <c r="B144" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>477</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>208</v>
@@ -7842,18 +7227,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>98</v>
       </c>
       <c r="B145" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>275</v>
@@ -7865,18 +7250,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>99</v>
       </c>
       <c r="B146" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>483</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>275</v>
@@ -7888,18 +7273,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>100</v>
       </c>
       <c r="B147" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>208</v>
@@ -7911,21 +7296,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>1003</v>
       </c>
       <c r="B148" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>489</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>11</v>
@@ -7934,18 +7319,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>101</v>
       </c>
       <c r="B149" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>275</v>
@@ -7957,18 +7342,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>102</v>
       </c>
       <c r="B150" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>495</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>245</v>
@@ -7980,21 +7365,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>103</v>
       </c>
       <c r="B151" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>11</v>
@@ -8003,18 +7388,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>104</v>
       </c>
       <c r="B152" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>249</v>
@@ -8026,18 +7411,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>255</v>
       </c>
       <c r="B153" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>50</v>
@@ -8049,18 +7434,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>297</v>
       </c>
       <c r="B154" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>507</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>50</v>
@@ -8069,21 +7454,21 @@
         <v>173</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>298</v>
       </c>
       <c r="B155" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>511</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>50</v>
@@ -8092,47 +7477,47 @@
         <v>173</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>105</v>
       </c>
       <c r="B156" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>173</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>106</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>519</v>
+        <v>1154</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>11</v>
@@ -8141,18 +7526,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>107</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>245</v>
@@ -8164,18 +7549,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>335</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>275</v>
@@ -8184,21 +7569,21 @@
         <v>173</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>108</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>249</v>
@@ -8210,18 +7595,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>109</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>275</v>
@@ -8233,18 +7618,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>110</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>208</v>
@@ -8256,21 +7641,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>111</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>11</v>
@@ -8279,21 +7664,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>112</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>11</v>
@@ -8302,18 +7687,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>113</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>275</v>
@@ -8325,18 +7710,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>114</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>201</v>
@@ -8348,18 +7733,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>115</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>208</v>
@@ -8371,18 +7756,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>116</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>208</v>
@@ -8394,18 +7779,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>117</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>249</v>
@@ -8414,21 +7799,21 @@
         <v>209</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>118</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>249</v>
@@ -8440,18 +7825,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>119</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>275</v>
@@ -8463,18 +7848,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>120</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>275</v>
@@ -8486,18 +7871,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>121</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>275</v>
@@ -8509,18 +7894,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>122</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>275</v>
@@ -8532,18 +7917,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>123</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>275</v>
@@ -8555,18 +7940,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>124</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>275</v>
@@ -8575,21 +7960,21 @@
         <v>173</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>125</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>275</v>
@@ -8601,18 +7986,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>16</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>50</v>
@@ -8624,18 +8009,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>17</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>50</v>
@@ -8644,21 +8029,21 @@
         <v>173</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>126</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>208</v>
@@ -8670,21 +8055,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>127</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>173</v>
@@ -8693,18 +8078,18 @@
         <v>284</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>128</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>245</v>
@@ -8716,18 +8101,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>129</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>245</v>
@@ -8739,18 +8124,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>130</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>208</v>
@@ -8762,18 +8147,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>131</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>208</v>
@@ -8782,21 +8167,21 @@
         <v>209</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>132</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>208</v>
@@ -8805,24 +8190,24 @@
         <v>209</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>133</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>11</v>
@@ -8831,18 +8216,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>134</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>208</v>
@@ -8851,44 +8236,44 @@
         <v>209</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>136</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>173</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>137</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>245</v>
@@ -8900,18 +8285,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>138</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>208</v>
@@ -8923,18 +8308,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>139</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>245</v>
@@ -8946,21 +8331,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>140</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>11</v>
@@ -8969,18 +8354,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>141</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>245</v>
@@ -8992,18 +8377,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>142</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>245</v>
@@ -9015,18 +8400,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>320</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>245</v>
@@ -9038,18 +8423,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>143</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>275</v>
@@ -9061,18 +8446,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>144</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>197</v>
@@ -9084,21 +8469,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>145</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>11</v>
@@ -9107,18 +8492,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>327</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>201</v>
@@ -9130,18 +8515,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>18</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>50</v>
@@ -9150,21 +8535,21 @@
         <v>209</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>19</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>50</v>
@@ -9173,21 +8558,21 @@
         <v>209</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>20</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>50</v>
@@ -9196,24 +8581,24 @@
         <v>209</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>146</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>11</v>
@@ -9222,41 +8607,41 @@
         <v>12</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>324</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>209</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>316</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>50</v>
@@ -9268,18 +8653,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>308</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>50</v>
@@ -9288,21 +8673,21 @@
         <v>209</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>147</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>50</v>
@@ -9311,21 +8696,21 @@
         <v>209</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>148</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>50</v>
@@ -9334,21 +8719,21 @@
         <v>209</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>149</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>50</v>
@@ -9357,21 +8742,21 @@
         <v>209</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>150</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>50</v>
@@ -9380,21 +8765,21 @@
         <v>209</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>151</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>50</v>
@@ -9403,21 +8788,21 @@
         <v>209</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>322</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>50</v>
@@ -9426,21 +8811,21 @@
         <v>209</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>315</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>50</v>
@@ -9452,18 +8837,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>152</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>50</v>
@@ -9472,21 +8857,21 @@
         <v>209</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>312</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>50</v>
@@ -9495,21 +8880,21 @@
         <v>209</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>313</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>50</v>
@@ -9518,21 +8903,21 @@
         <v>209</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>153</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>275</v>
@@ -9544,18 +8929,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>154</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>275</v>
@@ -9567,18 +8952,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>155</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>201</v>
@@ -9590,18 +8975,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>156</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>208</v>
@@ -9610,21 +8995,21 @@
         <v>209</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>157</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>208</v>
@@ -9633,21 +9018,21 @@
         <v>209</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>158</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>208</v>
@@ -9656,21 +9041,21 @@
         <v>209</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>159</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>208</v>
@@ -9679,21 +9064,21 @@
         <v>209</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>160</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>208</v>
@@ -9702,21 +9087,21 @@
         <v>209</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>161</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>208</v>
@@ -9725,21 +9110,21 @@
         <v>209</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>162</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>208</v>
@@ -9748,21 +9133,21 @@
         <v>209</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>163</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>208</v>
@@ -9771,21 +9156,21 @@
         <v>209</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>164</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>208</v>
@@ -9794,21 +9179,21 @@
         <v>209</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>165</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>249</v>
@@ -9817,21 +9202,21 @@
         <v>209</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>166</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>208</v>
@@ -9840,21 +9225,21 @@
         <v>209</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>167</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>208</v>
@@ -9863,21 +9248,21 @@
         <v>209</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>168</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>208</v>
@@ -9886,21 +9271,21 @@
         <v>209</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>169</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>208</v>
@@ -9909,21 +9294,21 @@
         <v>209</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>170</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>208</v>
@@ -9932,21 +9317,21 @@
         <v>209</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>171</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>208</v>
@@ -9955,21 +9340,21 @@
         <v>209</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>172</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>208</v>
@@ -9978,21 +9363,21 @@
         <v>209</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>173</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>208</v>
@@ -10001,21 +9386,21 @@
         <v>209</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>174</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>249</v>
@@ -10024,24 +9409,24 @@
         <v>209</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>175</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>11</v>
@@ -10050,21 +9435,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>176</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>11</v>
@@ -10073,21 +9458,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>177</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>11</v>
@@ -10096,18 +9481,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>178</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>208</v>
@@ -10119,18 +9504,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>179</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>208</v>
@@ -10139,21 +9524,21 @@
         <v>209</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>180</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>208</v>
@@ -10162,24 +9547,24 @@
         <v>209</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>1004</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>11</v>
@@ -10188,21 +9573,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>1005</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>11</v>
@@ -10211,21 +9596,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>1006</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>11</v>
@@ -10234,21 +9619,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>1007</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>11</v>
@@ -10257,18 +9642,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="250" spans="1:7">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>181</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>208</v>
@@ -10280,21 +9665,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>182</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>11</v>
@@ -10303,21 +9688,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>1002</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>11</v>
@@ -10326,18 +9711,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="253" spans="1:7">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>21</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>50</v>
@@ -10349,18 +9734,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>22</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>50</v>
@@ -10372,18 +9757,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>23</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>50</v>
@@ -10392,21 +9777,21 @@
         <v>173</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>183</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>208</v>
@@ -10418,18 +9803,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>184</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>208</v>
@@ -10441,18 +9826,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>185</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>208</v>
@@ -10461,21 +9846,21 @@
         <v>209</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>186</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>208</v>
@@ -10484,24 +9869,24 @@
         <v>209</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>187</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>11</v>
@@ -10510,21 +9895,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>188</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>11</v>
@@ -10533,18 +9918,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>328</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>208</v>
@@ -10556,18 +9941,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>189</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>249</v>
@@ -10579,18 +9964,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>336</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>245</v>
@@ -10599,24 +9984,24 @@
         <v>12</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>190</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>11</v>
@@ -10625,18 +10010,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>191</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>208</v>
@@ -10648,18 +10033,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>192</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>208</v>
@@ -10671,18 +10056,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>306</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>50</v>
@@ -10694,18 +10079,18 @@
         <v>170</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>307</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>50</v>
@@ -10717,18 +10102,18 @@
         <v>175</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>193</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>245</v>
@@ -10740,21 +10125,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>194</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>11</v>
@@ -10763,18 +10148,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>321</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>249</v>
@@ -10786,21 +10171,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>195</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>11</v>
@@ -10809,41 +10194,41 @@
         <v>12</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>196</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>173</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>197</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>245</v>
@@ -10855,18 +10240,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>198</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>208</v>
@@ -10875,21 +10260,21 @@
         <v>209</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>199</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>275</v>
@@ -10898,21 +10283,21 @@
         <v>209</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>200</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>208</v>
@@ -10921,24 +10306,24 @@
         <v>209</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>201</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>11</v>
@@ -10947,18 +10332,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>202</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>208</v>
@@ -10970,18 +10355,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>314</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>50</v>
@@ -10993,18 +10378,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>24</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>50</v>
@@ -11016,18 +10401,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>25</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>50</v>
@@ -11039,18 +10424,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>203</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>208</v>
@@ -11062,18 +10447,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>204</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>208</v>
@@ -11082,21 +10467,21 @@
         <v>209</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>205</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>208</v>
@@ -11105,24 +10490,24 @@
         <v>209</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>1000</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>11</v>
@@ -11131,18 +10516,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>206</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>245</v>
@@ -11154,18 +10539,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>207</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>249</v>
@@ -11174,21 +10559,21 @@
         <v>209</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>208</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>249</v>
@@ -11197,21 +10582,21 @@
         <v>209</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>209</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>249</v>
@@ -11220,24 +10605,24 @@
         <v>209</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>210</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>11</v>
@@ -11246,21 +10631,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="293" spans="1:7">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>211</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>11</v>
@@ -11269,18 +10654,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="294" spans="1:7">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>212</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>208</v>
@@ -11289,21 +10674,21 @@
         <v>173</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>213</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>201</v>
@@ -11315,21 +10700,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>214</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>11</v>
@@ -11338,18 +10723,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="297" spans="1:7">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>215</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>208</v>
@@ -11361,21 +10746,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="298" spans="1:7">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>216</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>11</v>
@@ -11384,18 +10769,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="299" spans="1:7">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>217</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>201</v>
@@ -11407,18 +10792,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="300" spans="1:7">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>218</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>201</v>
@@ -11430,18 +10815,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>334</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>208</v>
@@ -11450,21 +10835,21 @@
         <v>209</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>219</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>249</v>
@@ -11473,21 +10858,21 @@
         <v>209</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>220</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>208</v>
@@ -11496,21 +10881,21 @@
         <v>209</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>221</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>249</v>
@@ -11519,21 +10904,21 @@
         <v>209</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>222</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>208</v>
@@ -11542,21 +10927,21 @@
         <v>209</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>330</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>249</v>
@@ -11565,21 +10950,21 @@
         <v>209</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>223</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>208</v>
@@ -11588,21 +10973,21 @@
         <v>209</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>224</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>208</v>
@@ -11611,21 +10996,21 @@
         <v>209</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>225</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>249</v>
@@ -11634,21 +11019,21 @@
         <v>209</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="310" spans="1:7">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>226</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>208</v>
@@ -11657,21 +11042,21 @@
         <v>209</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="311" spans="1:7">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>227</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>249</v>
@@ -11680,24 +11065,24 @@
         <v>209</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="312" spans="1:7">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>228</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>11</v>
@@ -11706,41 +11091,41 @@
         <v>12</v>
       </c>
     </row>
-    <row r="313" spans="1:7">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>229</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>209</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="314" spans="1:7">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>317</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>50</v>
@@ -11752,18 +11137,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="315" spans="1:7">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>230</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>50</v>
@@ -11772,21 +11157,21 @@
         <v>209</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>231</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>50</v>
@@ -11795,21 +11180,21 @@
         <v>209</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="317" spans="1:7">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>232</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>50</v>
@@ -11818,21 +11203,21 @@
         <v>209</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="318" spans="1:7">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>233</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>50</v>
@@ -11841,21 +11226,21 @@
         <v>209</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="319" spans="1:7">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>234</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>50</v>
@@ -11864,21 +11249,21 @@
         <v>209</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="320" spans="1:7">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>323</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>50</v>
@@ -11887,21 +11272,21 @@
         <v>209</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="321" spans="1:7">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>309</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>50</v>
@@ -11910,21 +11295,21 @@
         <v>209</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="322" spans="1:7">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>235</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>50</v>
@@ -11933,21 +11318,21 @@
         <v>209</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="323" spans="1:7">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>325</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>50</v>
@@ -11956,21 +11341,21 @@
         <v>209</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="324" spans="1:7">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>236</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>50</v>
@@ -11979,21 +11364,21 @@
         <v>209</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="325" spans="1:7">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>237</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>208</v>
@@ -12005,18 +11390,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>238</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>208</v>
@@ -12025,21 +11410,21 @@
         <v>209</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="327" spans="1:7">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>239</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>208</v>
@@ -12048,21 +11433,21 @@
         <v>209</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="328" spans="1:7">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>295</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>245</v>
@@ -12074,44 +11459,44 @@
         <v>12</v>
       </c>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>240</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>209</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="330" spans="1:7">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>241</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>11</v>
@@ -12120,18 +11505,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>242</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>249</v>
@@ -12143,18 +11528,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>243</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>201</v>
@@ -12166,18 +11551,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>244</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>275</v>
@@ -12189,18 +11574,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>26</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>50</v>
@@ -12212,18 +11597,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>27</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>50</v>
@@ -12235,18 +11620,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="336" spans="1:7">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>245</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>208</v>
@@ -12258,21 +11643,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>246</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>11</v>
@@ -12281,21 +11666,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>247</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>11</v>
@@ -12304,18 +11689,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>248</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>201</v>
@@ -12327,18 +11712,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>249</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>249</v>
@@ -12350,18 +11735,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="341" spans="1:7">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>250</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>245</v>
@@ -12373,64 +11758,64 @@
         <v>12</v>
       </c>
     </row>
-    <row r="342" spans="1:7">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>135</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>173</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="343" spans="1:7">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>251</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>173</v>
       </c>
       <c r="G343" s="1" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="344" spans="1:7">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>252</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>208</v>
@@ -12442,18 +11827,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="345" spans="1:7">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>253</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>208</v>
@@ -12462,21 +11847,21 @@
         <v>209</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="346" spans="1:7">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>254</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>208</v>
@@ -12485,21 +11870,21 @@
         <v>209</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="347" spans="1:7">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>256</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>275</v>
@@ -12508,12 +11893,12 @@
         <v>173</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -12521,13 +11906,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 

--- a/pacenote_view.xlsx
+++ b/pacenote_view.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\devfiles\auto_media_pack_acg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B163406-D167-444C-AB17-495FC344A8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9DB99B-399B-4251-8777-DF07A084D7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="144" yWindow="1296" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2894,9 +2894,6 @@
     <t>start_stage,system_start_stage</t>
   </si>
   <si>
-    <t>比赛开始骚话</t>
-  </si>
-  <si>
     <t>steep</t>
   </si>
   <si>
@@ -3513,13 +3510,17 @@
   </si>
   <si>
     <t>手杀</t>
+  </si>
+  <si>
+    <t>比赛开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3530,6 +3531,14 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3554,9 +3563,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5858,7 +5868,7 @@
         <v>285</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>286</v>
@@ -6295,7 +6305,7 @@
         <v>345</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>286</v>
@@ -7514,7 +7524,7 @@
         <v>516</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>286</v>
@@ -10503,8 +10513,8 @@
       <c r="C287" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="D287" s="1" t="s">
-        <v>948</v>
+      <c r="D287" s="2" t="s">
+        <v>1154</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>323</v>
@@ -10521,13 +10531,13 @@
         <v>206</v>
       </c>
       <c r="B288" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="C288" s="1" t="s">
         <v>949</v>
       </c>
-      <c r="C288" s="1" t="s">
+      <c r="D288" s="1" t="s">
         <v>950</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>951</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>245</v>
@@ -10544,13 +10554,13 @@
         <v>207</v>
       </c>
       <c r="B289" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="C289" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="C289" s="1" t="s">
+      <c r="D289" s="1" t="s">
         <v>953</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>954</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>249</v>
@@ -10559,7 +10569,7 @@
         <v>209</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -10567,13 +10577,13 @@
         <v>208</v>
       </c>
       <c r="B290" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="C290" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="C290" s="1" t="s">
-        <v>957</v>
-      </c>
       <c r="D290" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>249</v>
@@ -10582,7 +10592,7 @@
         <v>209</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -10590,13 +10600,13 @@
         <v>209</v>
       </c>
       <c r="B291" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="C291" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="C291" s="1" t="s">
-        <v>959</v>
-      </c>
       <c r="D291" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>249</v>
@@ -10605,7 +10615,7 @@
         <v>209</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -10613,13 +10623,13 @@
         <v>210</v>
       </c>
       <c r="B292" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="C292" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="C292" s="1" t="s">
+      <c r="D292" s="1" t="s">
         <v>961</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>962</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>286</v>
@@ -10636,13 +10646,13 @@
         <v>211</v>
       </c>
       <c r="B293" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="C293" s="1" t="s">
         <v>963</v>
       </c>
-      <c r="C293" s="1" t="s">
+      <c r="D293" s="1" t="s">
         <v>964</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>965</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>286</v>
@@ -10659,10 +10669,10 @@
         <v>212</v>
       </c>
       <c r="B294" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="C294" s="1" t="s">
         <v>966</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>967</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>937</v>
@@ -10682,13 +10692,13 @@
         <v>213</v>
       </c>
       <c r="B295" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="C295" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="C295" s="1" t="s">
+      <c r="D295" s="1" t="s">
         <v>969</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>970</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>201</v>
@@ -10705,13 +10715,13 @@
         <v>214</v>
       </c>
       <c r="B296" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="C296" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="C296" s="1" t="s">
+      <c r="D296" s="1" t="s">
         <v>972</v>
-      </c>
-      <c r="D296" s="1" t="s">
-        <v>973</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>286</v>
@@ -10728,13 +10738,13 @@
         <v>215</v>
       </c>
       <c r="B297" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="C297" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="C297" s="1" t="s">
+      <c r="D297" s="1" t="s">
         <v>975</v>
-      </c>
-      <c r="D297" s="1" t="s">
-        <v>976</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>208</v>
@@ -10751,13 +10761,13 @@
         <v>216</v>
       </c>
       <c r="B298" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="C298" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="C298" s="1" t="s">
+      <c r="D298" s="1" t="s">
         <v>978</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>979</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>319</v>
@@ -10774,13 +10784,13 @@
         <v>217</v>
       </c>
       <c r="B299" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="C299" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="C299" s="1" t="s">
+      <c r="D299" s="1" t="s">
         <v>981</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>982</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>201</v>
@@ -10797,13 +10807,13 @@
         <v>218</v>
       </c>
       <c r="B300" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="C300" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="C300" s="1" t="s">
+      <c r="D300" s="1" t="s">
         <v>984</v>
-      </c>
-      <c r="D300" s="1" t="s">
-        <v>985</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>201</v>
@@ -10820,13 +10830,13 @@
         <v>334</v>
       </c>
       <c r="B301" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="C301" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="C301" s="1" t="s">
+      <c r="D301" s="1" t="s">
         <v>987</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>988</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>208</v>
@@ -10835,7 +10845,7 @@
         <v>209</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -10843,13 +10853,13 @@
         <v>219</v>
       </c>
       <c r="B302" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="C302" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="C302" s="1" t="s">
+      <c r="D302" s="1" t="s">
         <v>991</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>992</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>249</v>
@@ -10858,7 +10868,7 @@
         <v>209</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
@@ -10866,13 +10876,13 @@
         <v>220</v>
       </c>
       <c r="B303" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="C303" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="C303" s="1" t="s">
+      <c r="D303" s="1" t="s">
         <v>995</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>996</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>208</v>
@@ -10881,7 +10891,7 @@
         <v>209</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -10889,13 +10899,13 @@
         <v>221</v>
       </c>
       <c r="B304" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="C304" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="C304" s="1" t="s">
+      <c r="D304" s="1" t="s">
         <v>999</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>1000</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>249</v>
@@ -10904,7 +10914,7 @@
         <v>209</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -10912,13 +10922,13 @@
         <v>222</v>
       </c>
       <c r="B305" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C305" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="C305" s="1" t="s">
+      <c r="D305" s="1" t="s">
         <v>1003</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>1004</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>208</v>
@@ -10927,7 +10937,7 @@
         <v>209</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -10935,13 +10945,13 @@
         <v>330</v>
       </c>
       <c r="B306" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C306" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="C306" s="1" t="s">
+      <c r="D306" s="1" t="s">
         <v>1007</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>1008</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>249</v>
@@ -10950,7 +10960,7 @@
         <v>209</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
@@ -10958,13 +10968,13 @@
         <v>223</v>
       </c>
       <c r="B307" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C307" s="1" t="s">
         <v>1010</v>
       </c>
-      <c r="C307" s="1" t="s">
+      <c r="D307" s="1" t="s">
         <v>1011</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>1012</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>208</v>
@@ -10973,7 +10983,7 @@
         <v>209</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
@@ -10981,13 +10991,13 @@
         <v>224</v>
       </c>
       <c r="B308" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C308" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="C308" s="1" t="s">
+      <c r="D308" s="1" t="s">
         <v>1015</v>
-      </c>
-      <c r="D308" s="1" t="s">
-        <v>1016</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>208</v>
@@ -10996,7 +11006,7 @@
         <v>209</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -11004,13 +11014,13 @@
         <v>225</v>
       </c>
       <c r="B309" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C309" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="C309" s="1" t="s">
+      <c r="D309" s="1" t="s">
         <v>1019</v>
-      </c>
-      <c r="D309" s="1" t="s">
-        <v>1020</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>249</v>
@@ -11019,7 +11029,7 @@
         <v>209</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
@@ -11027,13 +11037,13 @@
         <v>226</v>
       </c>
       <c r="B310" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C310" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="C310" s="1" t="s">
+      <c r="D310" s="1" t="s">
         <v>1023</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>1024</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>208</v>
@@ -11042,7 +11052,7 @@
         <v>209</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
@@ -11050,13 +11060,13 @@
         <v>227</v>
       </c>
       <c r="B311" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C311" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="C311" s="1" t="s">
+      <c r="D311" s="1" t="s">
         <v>1027</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>1028</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>249</v>
@@ -11065,7 +11075,7 @@
         <v>209</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -11073,13 +11083,13 @@
         <v>228</v>
       </c>
       <c r="B312" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C312" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="C312" s="1" t="s">
+      <c r="D312" s="1" t="s">
         <v>1031</v>
-      </c>
-      <c r="D312" s="1" t="s">
-        <v>1032</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>437</v>
@@ -11096,13 +11106,13 @@
         <v>229</v>
       </c>
       <c r="B313" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C313" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="C313" s="1" t="s">
+      <c r="D313" s="1" t="s">
         <v>1034</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>1035</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>437</v>
@@ -11111,7 +11121,7 @@
         <v>209</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
@@ -11119,13 +11129,13 @@
         <v>317</v>
       </c>
       <c r="B314" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C314" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="C314" s="1" t="s">
+      <c r="D314" s="1" t="s">
         <v>1038</v>
-      </c>
-      <c r="D314" s="1" t="s">
-        <v>1039</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>50</v>
@@ -11142,13 +11152,13 @@
         <v>230</v>
       </c>
       <c r="B315" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C315" s="1" t="s">
         <v>1040</v>
       </c>
-      <c r="C315" s="1" t="s">
+      <c r="D315" s="1" t="s">
         <v>1041</v>
-      </c>
-      <c r="D315" s="1" t="s">
-        <v>1042</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>50</v>
@@ -11157,7 +11167,7 @@
         <v>209</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -11165,13 +11175,13 @@
         <v>231</v>
       </c>
       <c r="B316" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C316" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="C316" s="1" t="s">
+      <c r="D316" s="1" t="s">
         <v>1045</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>1046</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>50</v>
@@ -11180,7 +11190,7 @@
         <v>209</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
@@ -11188,13 +11198,13 @@
         <v>232</v>
       </c>
       <c r="B317" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C317" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="C317" s="1" t="s">
+      <c r="D317" s="1" t="s">
         <v>1049</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>1050</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>50</v>
@@ -11203,7 +11213,7 @@
         <v>209</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
@@ -11211,13 +11221,13 @@
         <v>233</v>
       </c>
       <c r="B318" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C318" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="C318" s="1" t="s">
+      <c r="D318" s="1" t="s">
         <v>1053</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>1054</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>50</v>
@@ -11226,7 +11236,7 @@
         <v>209</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
@@ -11234,13 +11244,13 @@
         <v>234</v>
       </c>
       <c r="B319" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C319" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="C319" s="1" t="s">
+      <c r="D319" s="1" t="s">
         <v>1057</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>1058</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>50</v>
@@ -11249,7 +11259,7 @@
         <v>209</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
@@ -11257,13 +11267,13 @@
         <v>323</v>
       </c>
       <c r="B320" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C320" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="C320" s="1" t="s">
+      <c r="D320" s="1" t="s">
         <v>1061</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>1062</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>50</v>
@@ -11272,7 +11282,7 @@
         <v>209</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
@@ -11280,13 +11290,13 @@
         <v>309</v>
       </c>
       <c r="B321" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C321" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="C321" s="1" t="s">
+      <c r="D321" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>1066</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>50</v>
@@ -11295,7 +11305,7 @@
         <v>209</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
@@ -11303,13 +11313,13 @@
         <v>235</v>
       </c>
       <c r="B322" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C322" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="C322" s="1" t="s">
+      <c r="D322" s="1" t="s">
         <v>1069</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>1070</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>50</v>
@@ -11318,7 +11328,7 @@
         <v>209</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
@@ -11326,13 +11336,13 @@
         <v>325</v>
       </c>
       <c r="B323" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C323" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="C323" s="1" t="s">
+      <c r="D323" s="1" t="s">
         <v>1073</v>
-      </c>
-      <c r="D323" s="1" t="s">
-        <v>1074</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>50</v>
@@ -11341,7 +11351,7 @@
         <v>209</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
@@ -11349,13 +11359,13 @@
         <v>236</v>
       </c>
       <c r="B324" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C324" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="C324" s="1" t="s">
+      <c r="D324" s="1" t="s">
         <v>1077</v>
-      </c>
-      <c r="D324" s="1" t="s">
-        <v>1078</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>50</v>
@@ -11364,7 +11374,7 @@
         <v>209</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -11372,13 +11382,13 @@
         <v>237</v>
       </c>
       <c r="B325" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C325" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="C325" s="1" t="s">
+      <c r="D325" s="1" t="s">
         <v>1081</v>
-      </c>
-      <c r="D325" s="1" t="s">
-        <v>1082</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>208</v>
@@ -11395,13 +11405,13 @@
         <v>238</v>
       </c>
       <c r="B326" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C326" s="1" t="s">
         <v>1083</v>
       </c>
-      <c r="C326" s="1" t="s">
+      <c r="D326" s="1" t="s">
         <v>1084</v>
-      </c>
-      <c r="D326" s="1" t="s">
-        <v>1085</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>208</v>
@@ -11410,7 +11420,7 @@
         <v>209</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -11418,13 +11428,13 @@
         <v>239</v>
       </c>
       <c r="B327" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C327" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="C327" s="1" t="s">
+      <c r="D327" s="1" t="s">
         <v>1088</v>
-      </c>
-      <c r="D327" s="1" t="s">
-        <v>1089</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>208</v>
@@ -11433,7 +11443,7 @@
         <v>209</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -11441,13 +11451,13 @@
         <v>295</v>
       </c>
       <c r="B328" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C328" s="1" t="s">
         <v>1091</v>
       </c>
-      <c r="C328" s="1" t="s">
+      <c r="D328" s="1" t="s">
         <v>1092</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>1093</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>245</v>
@@ -11464,13 +11474,13 @@
         <v>240</v>
       </c>
       <c r="B329" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C329" s="1" t="s">
         <v>1094</v>
       </c>
-      <c r="C329" s="1" t="s">
+      <c r="D329" s="1" t="s">
         <v>1095</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>1096</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>290</v>
@@ -11479,7 +11489,7 @@
         <v>209</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
@@ -11487,13 +11497,13 @@
         <v>241</v>
       </c>
       <c r="B330" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C330" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="C330" s="1" t="s">
+      <c r="D330" s="1" t="s">
         <v>1099</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>1100</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>290</v>
@@ -11510,13 +11520,13 @@
         <v>242</v>
       </c>
       <c r="B331" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C331" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="C331" s="1" t="s">
+      <c r="D331" s="1" t="s">
         <v>1102</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>1103</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>249</v>
@@ -11533,13 +11543,13 @@
         <v>243</v>
       </c>
       <c r="B332" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C332" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="C332" s="1" t="s">
+      <c r="D332" s="1" t="s">
         <v>1105</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>1106</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>201</v>
@@ -11559,10 +11569,10 @@
         <v>575</v>
       </c>
       <c r="C333" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>1107</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>1108</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>275</v>
@@ -11579,13 +11589,13 @@
         <v>26</v>
       </c>
       <c r="B334" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C334" s="1" t="s">
         <v>1109</v>
       </c>
-      <c r="C334" s="1" t="s">
+      <c r="D334" s="1" t="s">
         <v>1110</v>
-      </c>
-      <c r="D334" s="1" t="s">
-        <v>1111</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>50</v>
@@ -11602,13 +11612,13 @@
         <v>27</v>
       </c>
       <c r="B335" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C335" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="C335" s="1" t="s">
+      <c r="D335" s="1" t="s">
         <v>1113</v>
-      </c>
-      <c r="D335" s="1" t="s">
-        <v>1114</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>50</v>
@@ -11625,13 +11635,13 @@
         <v>245</v>
       </c>
       <c r="B336" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C336" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="C336" s="1" t="s">
+      <c r="D336" s="1" t="s">
         <v>1116</v>
-      </c>
-      <c r="D336" s="1" t="s">
-        <v>1117</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>208</v>
@@ -11648,13 +11658,13 @@
         <v>246</v>
       </c>
       <c r="B337" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C337" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="C337" s="1" t="s">
+      <c r="D337" s="1" t="s">
         <v>1119</v>
-      </c>
-      <c r="D337" s="1" t="s">
-        <v>1120</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>286</v>
@@ -11671,13 +11681,13 @@
         <v>247</v>
       </c>
       <c r="B338" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C338" s="1" t="s">
         <v>1121</v>
       </c>
-      <c r="C338" s="1" t="s">
+      <c r="D338" s="1" t="s">
         <v>1122</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>1123</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>290</v>
@@ -11694,13 +11704,13 @@
         <v>248</v>
       </c>
       <c r="B339" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C339" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="C339" s="1" t="s">
+      <c r="D339" s="1" t="s">
         <v>1125</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>1126</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>201</v>
@@ -11717,13 +11727,13 @@
         <v>249</v>
       </c>
       <c r="B340" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C340" s="1" t="s">
         <v>1127</v>
       </c>
-      <c r="C340" s="1" t="s">
+      <c r="D340" s="1" t="s">
         <v>1128</v>
-      </c>
-      <c r="D340" s="1" t="s">
-        <v>1129</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>249</v>
@@ -11740,13 +11750,13 @@
         <v>250</v>
       </c>
       <c r="B341" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C341" s="1" t="s">
         <v>1130</v>
       </c>
-      <c r="C341" s="1" t="s">
+      <c r="D341" s="1" t="s">
         <v>1131</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>1132</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>245</v>
@@ -11763,13 +11773,13 @@
         <v>135</v>
       </c>
       <c r="B342" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C342" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="C342" s="1" t="s">
+      <c r="D342" s="1" t="s">
         <v>1134</v>
-      </c>
-      <c r="D342" s="1" t="s">
-        <v>1135</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>437</v>
@@ -11778,7 +11788,7 @@
         <v>173</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
@@ -11786,13 +11796,13 @@
         <v>251</v>
       </c>
       <c r="B343" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C343" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="C343" s="1" t="s">
+      <c r="D343" s="1" t="s">
         <v>1138</v>
-      </c>
-      <c r="D343" s="1" t="s">
-        <v>1139</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>286</v>
@@ -11809,13 +11819,13 @@
         <v>252</v>
       </c>
       <c r="B344" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C344" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="C344" s="1" t="s">
+      <c r="D344" s="1" t="s">
         <v>1141</v>
-      </c>
-      <c r="D344" s="1" t="s">
-        <v>1142</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>208</v>
@@ -11832,13 +11842,13 @@
         <v>253</v>
       </c>
       <c r="B345" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C345" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="C345" s="1" t="s">
+      <c r="D345" s="1" t="s">
         <v>1144</v>
-      </c>
-      <c r="D345" s="1" t="s">
-        <v>1145</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>208</v>
@@ -11847,7 +11857,7 @@
         <v>209</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
@@ -11855,13 +11865,13 @@
         <v>254</v>
       </c>
       <c r="B346" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C346" s="1" t="s">
         <v>1146</v>
       </c>
-      <c r="C346" s="1" t="s">
+      <c r="D346" s="1" t="s">
         <v>1147</v>
-      </c>
-      <c r="D346" s="1" t="s">
-        <v>1148</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>208</v>
@@ -11870,7 +11880,7 @@
         <v>209</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
@@ -11878,13 +11888,13 @@
         <v>256</v>
       </c>
       <c r="B347" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C347" s="1" t="s">
         <v>1149</v>
       </c>
-      <c r="C347" s="1" t="s">
+      <c r="D347" s="1" t="s">
         <v>1150</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>1151</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>275</v>
